--- a/Эконом Стоимость.xlsx
+++ b/Эконом Стоимость.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="62">
   <si>
     <t>предмет</t>
   </si>
@@ -44,6 +44,162 @@
     <t>ссылка</t>
   </si>
   <si>
+    <t>Опора для 10 кВ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Опоры (стойки) ЛЭП СНВ 7-13 </t>
+  </si>
+  <si>
+    <t>17 опор</t>
+  </si>
+  <si>
+    <t>2 100 000 рублей (меж.опорами 70 метров)</t>
+  </si>
+  <si>
+    <t>https://psk-energo.ru/catalog/energeticheskoe-stroitelstvo/oporyi-lep/stojki-snv/stoyka-snv-7-13</t>
+  </si>
+  <si>
+    <t>Провод (10 кВ)</t>
+  </si>
+  <si>
+    <t>АС-120/19</t>
+  </si>
+  <si>
+    <t>1127 метров</t>
+  </si>
+  <si>
+    <t>281 750 рублей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://energopostavkabel.ru/katalog-produktsii/as-120-19 </t>
+  </si>
+  <si>
+    <t>Провод для 0,4 кВ</t>
+  </si>
+  <si>
+    <t>СИП-4 4х120</t>
+  </si>
+  <si>
+    <t>2597 метров</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 337 300 рублей </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ruzkabel.ru/sip-4-4x120/ </t>
+  </si>
+  <si>
+    <t>Опора для 0,4 кВ</t>
+  </si>
+  <si>
+    <t>Стойка-Опоры СВ 95-2</t>
+  </si>
+  <si>
+    <t>75 опор</t>
+  </si>
+  <si>
+    <t>742 000 рублей</t>
+  </si>
+  <si>
+    <t>https://tula.psk-energo.ru/catalog/energeticheskoe-stroitelstvo/oporyi-lep/stojki-sv/stoyka-sv-95-2</t>
+  </si>
+  <si>
+    <t>Дизельный Генератор</t>
+  </si>
+  <si>
+    <t>Woling AD 1000-T400 в контейнере</t>
+  </si>
+  <si>
+    <t>3 шт</t>
+  </si>
+  <si>
+    <t>22 500 000 рублей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://woling.ru </t>
+  </si>
+  <si>
+    <t>Солнечные панели</t>
+  </si>
+  <si>
+    <t>Jinko 600 W N-Type Solar Panel</t>
+  </si>
+  <si>
+    <t>12 000 шт (1 по 600 Вт)</t>
+  </si>
+  <si>
+    <t>122 360 000 рублей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ветрогенераторы </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cemi dk 1 mw </t>
+  </si>
+  <si>
+    <t>72 090 000 рублей ( монтаж 40 000 000)</t>
+  </si>
+  <si>
+    <t>https://ru.made-in-china.com</t>
+  </si>
+  <si>
+    <t>Трансформатор 1000кВа</t>
+  </si>
+  <si>
+    <t>ТМГ-1000</t>
+  </si>
+  <si>
+    <t>2 шт</t>
+  </si>
+  <si>
+    <t>1 800 000 рублей</t>
+  </si>
+  <si>
+    <t>https://etm.ru</t>
+  </si>
+  <si>
+    <t>Трансформатор 630 кВа</t>
+  </si>
+  <si>
+    <t>ТМГ-630</t>
+  </si>
+  <si>
+    <t>4 шт</t>
+  </si>
+  <si>
+    <t>1 700 000 рублей</t>
+  </si>
+  <si>
+    <t>https://uzeu.ru</t>
+  </si>
+  <si>
+    <t>Опора для 110 кВ</t>
+  </si>
+  <si>
+    <t>Промежуточная опора ПС110-10В П110-1</t>
+  </si>
+  <si>
+    <t>1415 опор</t>
+  </si>
+  <si>
+    <t>438 650 000 рублей (за 283 км меж.опор 200м)</t>
+  </si>
+  <si>
+    <t>https://www.tseh5-kazan.ru/goods/238133064-promezhutochnaya_opora_ps110_10v_p110_1</t>
+  </si>
+  <si>
+    <t>Кабель (0,4 кВ)</t>
+  </si>
+  <si>
+    <t>ПвПг 1x185/35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 кабелей </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://rscable.ru/product/38270/ </t>
+  </si>
+  <si>
     <t>Провод (110 кВ)</t>
   </si>
   <si>
@@ -57,51 +213,6 @@
   </si>
   <si>
     <t>https://dielec.ru/cable/product_bare-electrical-wires_ask2u-240-56</t>
-  </si>
-  <si>
-    <t>Провод (10 кВ)</t>
-  </si>
-  <si>
-    <t>АС-120/19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://energopostavkabel.ru/katalog-produktsii/as-120-19 </t>
-  </si>
-  <si>
-    <t>Кабель (0,4 кВ)</t>
-  </si>
-  <si>
-    <t>ПвПг 1x185/35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 кабелей </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://rscable.ru/product/38270/ </t>
-  </si>
-  <si>
-    <t>Опора для 10 кВ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Опоры (стойки) ЛЭП СНВ 7-13 </t>
-  </si>
-  <si>
-    <t>30 000 рублей (за 1 шт)</t>
-  </si>
-  <si>
-    <t>https://psk-energo.ru/catalog/energeticheskoe-stroitelstvo/oporyi-lep/stojki-snv/stoyka-snv-7-13</t>
-  </si>
-  <si>
-    <t>Опора для 110 кВ</t>
-  </si>
-  <si>
-    <t>Промежуточная опора ПС110-10В П110-1</t>
-  </si>
-  <si>
-    <t>310 000 рублей (за 1 шт)</t>
-  </si>
-  <si>
-    <t>https://www.tseh5-kazan.ru/goods/238133064-promezhutochnaya_opora_ps110_10v_p110_1</t>
   </si>
 </sst>
 </file>
@@ -114,7 +225,7 @@
     <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,6 +253,20 @@
       <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial Black"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -602,128 +727,128 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -733,7 +858,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1269,14 +1403,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:H50"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="22.2222222222222" customWidth="1"/>
     <col min="2" max="2" width="37.5555555555556" customWidth="1"/>
-    <col min="3" max="3" width="25.7777777777778" customWidth="1"/>
-    <col min="4" max="4" width="38.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="80.8888888888889" customWidth="1"/>
+    <col min="3" max="3" width="33.8888888888889" customWidth="1"/>
+    <col min="4" max="4" width="40.5555555555556" customWidth="1"/>
+    <col min="5" max="5" width="82.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.4" spans="1:5">
@@ -1296,7 +1430,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1312,6 +1446,7 @@
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
@@ -1320,59 +1455,195 @@
       <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="C3" t="s">
         <v>12</v>
       </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" ht="21" spans="1:6">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
+      </c>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" ht="16" customHeight="1" spans="1:4">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" t="s">
+        <v>51</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" t="s">
+        <v>54</v>
+      </c>
+      <c r="C49" t="s">
+        <v>55</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" t="s">
+        <v>59</v>
+      </c>
+      <c r="D50" t="s">
+        <v>60</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" display="https://energopostavkabel.ru/katalog-produktsii/as-120-19 "/>
-    <hyperlink ref="E4" r:id="rId2" display="https://rscable.ru/product/38270/ "/>
-    <hyperlink ref="E2" r:id="rId3" display="https://dielec.ru/cable/product_bare-electrical-wires_ask2u-240-56"/>
-    <hyperlink ref="E5" r:id="rId4" display="https://psk-energo.ru/catalog/energeticheskoe-stroitelstvo/oporyi-lep/stojki-snv/stoyka-snv-7-13"/>
-    <hyperlink ref="E6" r:id="rId5" display="https://www.tseh5-kazan.ru/goods/238133064-promezhutochnaya_opora_ps110_10v_p110_1"/>
+    <hyperlink ref="E49" r:id="rId2" display="https://rscable.ru/product/38270/ "/>
+    <hyperlink ref="E50" r:id="rId3" display="https://dielec.ru/cable/product_bare-electrical-wires_ask2u-240-56"/>
+    <hyperlink ref="E2" r:id="rId4" display="https://psk-energo.ru/catalog/energeticheskoe-stroitelstvo/oporyi-lep/stojki-snv/stoyka-snv-7-13"/>
+    <hyperlink ref="E48" r:id="rId5" display="https://www.tseh5-kazan.ru/goods/238133064-promezhutochnaya_opora_ps110_10v_p110_1"/>
+    <hyperlink ref="E4" r:id="rId6" display="https://ruzkabel.ru/sip-4-4x120/ "/>
+    <hyperlink ref="E5" r:id="rId7" display="https://tula.psk-energo.ru/catalog/energeticheskoe-stroitelstvo/oporyi-lep/stojki-sv/stoyka-sv-95-2"/>
+    <hyperlink ref="E6" r:id="rId8" display="https://woling.ru "/>
+    <hyperlink ref="E8" r:id="rId9" display="https://ru.made-in-china.com"/>
+    <hyperlink ref="E9" r:id="rId10" display="https://etm.ru"/>
+    <hyperlink ref="E10" r:id="rId11" display="https://uzeu.ru"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
